--- a/data/output/2025/evaluasi_74.xlsx
+++ b/data/output/2025/evaluasi_74.xlsx
@@ -24,6 +24,7 @@
     <sheet name="7404" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="7415" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="7405" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7403" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,6 +1192,230 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.53435299956443</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-11.61606837786946</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3981598778079767</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8.231037505188077</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-10.38287305622667</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.289543818458998</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.698901269529332</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.168938920894942</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1490,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-21.27074789076788</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2807295269131843</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>43.31603463279929</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.550253964538614</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8281143598475436</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,6 +1704,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.245991810051703</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.747123951023843</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>45.63412972417556</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.234850281523336</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.898758472973728</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1181855423923175</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.841661006483497</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.356605904639974</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.414062192942304</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,6 +2086,202 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3233486577431667</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>42.68830673557007</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.02579550355305</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.883472893470149</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04013584439641406</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.462282911363724</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5466985916960373</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1483,7 +2296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +2356,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.687415985170031</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9357650897105644</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>51.69175453240319</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.60140141119979</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.47298969210488</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.423981146832229</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5686111936159193</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3862822687017093</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.356605904639969</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1557,7 +2622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,18 +2696,354 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-3.598368613890484</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8651884455938079</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>40.31338015022344</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.0229460601538</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05765029847659599</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.895009829436885</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.030588954819921</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.480486602688047</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6960272038489823</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3533065520171243</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.736731919308568</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.224915664822162</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>-2.839257937488253</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1659,7 +3060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,6 +3120,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4368133768256638</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-13.43605037946372</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28.37187486521228</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2599598579446669</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.84449254876382</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.692558831708256</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.049425196825857</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1037026698718913</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.164191766067803</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1733,7 +3386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +3446,584 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>44.78743670742043</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15.19746797958764</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.83528386701859</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.17056136300794</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3467565173697862</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.954493288431271</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.007755341042834876</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3629136898886259</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7405</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.741844922679741</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-7.992753877292598</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.028744726523259</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>41.36572660809617</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.762053997543985</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.548351086537393</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.470445619662215</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.326054895584313</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3520583057963077</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3629136898886049</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.110500170571239</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1807,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +4602,258 @@
       <c r="F20" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-3.030427888593502</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.860529469654567</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>95.56440706128787</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>17.67303956046889</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1349551856594084</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-17.19231543738562</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.975366589852897</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.19632739398721</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.4921487931381564</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2385,7 +4868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2585,6 +5068,174 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8434886010394019</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6347930781615044</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>39.13224846967213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1124123495870025</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4162279313888329</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.6036923790644574</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2599,7 +5250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,6 +5394,202 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2671435893461203</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.203143269664763</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>38.55875023499924</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1070446455870635</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04049988428604152</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5616521328388715</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.633913893936878</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2757,7 +5604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3027,20 +5874,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.545805639259911</v>
+        <v>-8.334468990803469</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3055,18 +5902,242 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>1.490030173246911</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.41696805609301</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20.46725962978195</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1506620633631414</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02008987579938018</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.092592357685445</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.654016441732819</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.545805639259911</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10.94833208068958</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3083,7 +6154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3339,6 +6410,258 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.179145444241129</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>49.90252874603075</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01462203405321114</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.61220998505427</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.945423045011486</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.199709657527673</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1177022768632001</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.04013584439642508</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.143612792185696</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3353,7 +6676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3847,18 +7170,382 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>-5.295053145359936</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2464161092489385</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>41.38855243815168</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.198337129561139</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.08613466754705035</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-10.65033959873448</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.642394820504019</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.835725341098728</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.065838414628579</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.04171185450908794</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.043448880875002</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.652121038686402</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.490480197915626</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>2.283574950916119</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3875,7 +7562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4047,6 +7734,118 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>58.57141685893266</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1518660723374299</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3344865308396306</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1641752469383597</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4061,7 +7860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4180,6 +7979,174 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-14.15710577232027</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.211998127693518</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>27.2032976008203</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04061738424048018</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3629136898886063</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.087032875924838</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
